--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -826,16 +826,19 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9713,0.0026,0.0079,0.0014</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9712,0.0026,0.0079,0.0014</t>
   </si>
   <si>
     <t>0.0044,0.0084,0.0006,0.9985</t>
   </si>
   <si>
-    <t>0.9835,0.0024,0.0006,0.0040</t>
-  </si>
-  <si>
-    <t>0.1443,0.0024,0.0041,0.9148</t>
+    <t>0.9835,0.0024,0.0006,0.0041</t>
+  </si>
+  <si>
+    <t>0.1436,0.0024,0.0042,0.9154</t>
   </si>
   <si>
     <t>0.9946,0.0020,0.0012,0.0003</t>
@@ -856,28 +859,28 @@
     <t>0.9913,0.0072,0.0012,0.0005</t>
   </si>
   <si>
-    <t>0.9955,0.0013,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0019,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.8602,0.0078,0.1134,0.0015</t>
-  </si>
-  <si>
-    <t>0.0219,0.0146,0.9697,0.0010</t>
-  </si>
-  <si>
-    <t>0.3162,0.0004,0.8265,0.0000</t>
-  </si>
-  <si>
-    <t>0.0537,0.0105,0.9445,0.0010</t>
-  </si>
-  <si>
-    <t>0.8073,0.0007,0.2257,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.9981,0.0157,0.0006</t>
+    <t>0.9954,0.0013,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9953,0.0019,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.8595,0.0077,0.1142,0.0015</t>
+  </si>
+  <si>
+    <t>0.0218,0.0145,0.9698,0.0010</t>
+  </si>
+  <si>
+    <t>0.3147,0.0004,0.8276,0.0000</t>
+  </si>
+  <si>
+    <t>0.0535,0.0105,0.9446,0.0010</t>
+  </si>
+  <si>
+    <t>0.8059,0.0007,0.2276,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9980,0.0157,0.0006</t>
   </si>
   <si>
     <t>0.0027,0.9971,0.0058,0.0009</t>
@@ -889,55 +892,55 @@
     <t>0.0030,0.9954,0.0071,0.0015</t>
   </si>
   <si>
-    <t>0.0009,0.9995,0.0129,0.0000</t>
-  </si>
-  <si>
-    <t>0.4559,0.0025,0.6382,0.0018</t>
-  </si>
-  <si>
-    <t>0.1495,0.0101,0.8683,0.0017</t>
-  </si>
-  <si>
-    <t>0.0241,0.0004,0.9889,0.0000</t>
-  </si>
-  <si>
-    <t>0.0247,0.0027,0.9817,0.0003</t>
-  </si>
-  <si>
-    <t>0.0376,0.0015,0.9784,0.0003</t>
-  </si>
-  <si>
-    <t>0.0747,0.0010,0.9572,0.0002</t>
+    <t>0.0009,0.9995,0.0130,0.0000</t>
+  </si>
+  <si>
+    <t>0.4543,0.0025,0.6399,0.0018</t>
+  </si>
+  <si>
+    <t>0.1487,0.0101,0.8692,0.0017</t>
+  </si>
+  <si>
+    <t>0.0240,0.0004,0.9889,0.0000</t>
+  </si>
+  <si>
+    <t>0.0246,0.0027,0.9817,0.0003</t>
+  </si>
+  <si>
+    <t>0.0373,0.0015,0.9785,0.0003</t>
+  </si>
+  <si>
+    <t>0.0743,0.0010,0.9574,0.0002</t>
   </si>
   <si>
     <t>0.0143,0.0010,0.9905,0.0003</t>
   </si>
   <si>
-    <t>0.7358,0.1415,0.0539,0.0012</t>
-  </si>
-  <si>
-    <t>0.8124,0.3159,0.0101,0.0018</t>
+    <t>0.7356,0.1411,0.0543,0.0012</t>
+  </si>
+  <si>
+    <t>0.8121,0.3156,0.0102,0.0018</t>
   </si>
   <si>
     <t>0.0047,0.0007,0.9968,0.0004</t>
   </si>
   <si>
-    <t>0.0179,0.3021,0.8382,0.0015</t>
-  </si>
-  <si>
-    <t>0.9319,0.0064,0.0382,0.0008</t>
-  </si>
-  <si>
-    <t>0.7939,0.0221,0.1225,0.0013</t>
-  </si>
-  <si>
-    <t>0.4003,0.7220,0.0232,0.0007</t>
-  </si>
-  <si>
-    <t>0.0069,0.9764,0.4440,0.0016</t>
-  </si>
-  <si>
-    <t>0.0010,0.7551,0.9412,0.0004</t>
+    <t>0.0179,0.3007,0.8391,0.0015</t>
+  </si>
+  <si>
+    <t>0.9315,0.0064,0.0385,0.0008</t>
+  </si>
+  <si>
+    <t>0.7927,0.0221,0.1235,0.0013</t>
+  </si>
+  <si>
+    <t>0.4003,0.7215,0.0234,0.0007</t>
+  </si>
+  <si>
+    <t>0.0068,0.9763,0.4451,0.0016</t>
+  </si>
+  <si>
+    <t>0.0010,0.7549,0.9412,0.0004</t>
   </si>
   <si>
     <t>0.0017,0.0030,0.9971,0.0012</t>
@@ -946,10 +949,10 @@
     <t>0.0109,0.0777,0.9644,0.0013</t>
   </si>
   <si>
-    <t>0.1577,0.0022,0.8635,0.0030</t>
-  </si>
-  <si>
-    <t>0.0006,0.7788,0.9137,0.0013</t>
+    <t>0.1567,0.0022,0.8645,0.0030</t>
+  </si>
+  <si>
+    <t>0.0006,0.7778,0.9142,0.0013</t>
   </si>
   <si>
     <t>0.0012,0.9916,0.0121,0.0026</t>
@@ -961,43 +964,43 @@
     <t>0.0004,0.8502,0.0013,0.9468</t>
   </si>
   <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0117,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0057,0.0001</t>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0118,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0058,0.0001</t>
   </si>
   <si>
     <t>0.0004,0.0113,0.9962,0.0015</t>
   </si>
   <si>
-    <t>0.0009,0.1851,0.9884,0.0016</t>
+    <t>0.0009,0.1850,0.9884,0.0016</t>
   </si>
   <si>
     <t>0.0088,0.0043,0.9894,0.0007</t>
   </si>
   <si>
-    <t>0.0261,0.0002,0.9903,0.0001</t>
+    <t>0.0260,0.0002,0.9903,0.0001</t>
   </si>
   <si>
     <t>0.0098,0.0014,0.9923,0.0001</t>
   </si>
   <si>
-    <t>0.0318,0.0155,0.9578,0.0011</t>
-  </si>
-  <si>
-    <t>0.9808,0.0078,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.9815,0.0006,0.0140,0.0001</t>
-  </si>
-  <si>
-    <t>0.9718,0.0159,0.0094,0.0039</t>
-  </si>
-  <si>
-    <t>0.4371,0.0017,0.6275,0.0004</t>
+    <t>0.0317,0.0155,0.9579,0.0011</t>
+  </si>
+  <si>
+    <t>0.9808,0.0078,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.9814,0.0006,0.0141,0.0001</t>
+  </si>
+  <si>
+    <t>0.9717,0.0160,0.0095,0.0039</t>
+  </si>
+  <si>
+    <t>0.4356,0.0017,0.6291,0.0004</t>
   </si>
   <si>
     <t>0.9894,0.0004,0.0058,0.0001</t>
@@ -1009,7 +1012,7 @@
     <t>0.9947,0.0008,0.0016,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.9990,0.8874,0.0000</t>
+    <t>0.0000,0.9990,0.8877,0.0000</t>
   </si>
   <si>
     <t>0.0004,0.1465,0.9977,0.0003</t>
@@ -1018,37 +1021,34 @@
     <t>0.0022,0.0163,0.9926,0.0012</t>
   </si>
   <si>
-    <t>0.0003,0.9833,0.8724,0.0005</t>
+    <t>0.0003,0.9833,0.8725,0.0005</t>
   </si>
   <si>
     <t>0.0004,0.0004,0.9994,0.0003</t>
   </si>
   <si>
-    <t>0.0014,0.9989,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9840,0.0002,0.0150,0.0000</t>
-  </si>
-  <si>
-    <t>0.1306,0.0258,0.8524,0.0022</t>
+    <t>0.0014,0.9989,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.9839,0.0002,0.0152,0.0000</t>
+  </si>
+  <si>
+    <t>0.1300,0.0257,0.8532,0.0022</t>
   </si>
   <si>
     <t>0.0137,0.0030,0.9899,0.0003</t>
   </si>
   <si>
-    <t>0.0004,0.8492,0.9783,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.9263,0.9793,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.3196,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9834,0.9621,0.0001</t>
+    <t>0.0004,0.8487,0.9783,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.9262,0.9793,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.3206,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9834,0.9622,0.0001</t>
   </si>
   <si>
     <t>0.0014,0.0045,0.0011,0.9996</t>
@@ -1063,34 +1063,34 @@
     <t>0.0029,0.0018,0.0010,0.9995</t>
   </si>
   <si>
-    <t>0.0320,0.0021,0.0025,0.9942</t>
+    <t>0.0319,0.0021,0.0025,0.9942</t>
   </si>
   <si>
     <t>0.0006,0.0035,0.0020,0.9998</t>
   </si>
   <si>
-    <t>0.0001,0.9977,0.8732,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9192,0.9917,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9390,0.8167,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.5048,0.9913,0.0004</t>
+    <t>0.0001,0.9977,0.8738,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9191,0.9917,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9388,0.8171,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.5046,0.9913,0.0004</t>
   </si>
   <si>
     <t>0.0000,0.9919,0.9876,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9921,0.6808,0.0002</t>
+    <t>0.0002,0.9921,0.6816,0.0002</t>
   </si>
   <si>
     <t>0.9939,0.0062,0.0005,0.0002</t>
   </si>
   <si>
-    <t>0.9835,0.0151,0.0021,0.0003</t>
+    <t>0.9835,0.0152,0.0021,0.0003</t>
   </si>
   <si>
     <t>0.9783,0.0319,0.0006,0.0001</t>
@@ -1123,7 +1123,7 @@
     <t>0.9972,0.0011,0.0004,0.0003</t>
   </si>
   <si>
-    <t>0.9882,0.0059,0.0012,0.0010</t>
+    <t>0.9882,0.0058,0.0012,0.0010</t>
   </si>
   <si>
     <t>0.9987,0.0009,0.0002,0.0000</t>
@@ -1132,19 +1132,19 @@
     <t>0.9960,0.0017,0.0006,0.0005</t>
   </si>
   <si>
-    <t>0.9930,0.0017,0.0016,0.0002</t>
+    <t>0.9930,0.0017,0.0017,0.0002</t>
   </si>
   <si>
     <t>0.0030,0.0002,0.9985,0.0000</t>
   </si>
   <si>
-    <t>0.0201,0.0015,0.9862,0.0002</t>
-  </si>
-  <si>
-    <t>0.9696,0.0001,0.0387,0.0000</t>
-  </si>
-  <si>
-    <t>0.0320,0.0011,0.9801,0.0001</t>
+    <t>0.0200,0.0015,0.9862,0.0002</t>
+  </si>
+  <si>
+    <t>0.9694,0.0001,0.0390,0.0000</t>
+  </si>
+  <si>
+    <t>0.0319,0.0011,0.9802,0.0001</t>
   </si>
   <si>
     <t>0.0002,0.9998,0.0003,0.0001</t>
@@ -1153,34 +1153,34 @@
     <t>0.0001,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.2747,0.8651,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.0410,0.9735,0.0141,0.0016</t>
+    <t>0.2744,0.8651,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.0409,0.9735,0.0142,0.0016</t>
   </si>
   <si>
     <t>0.0004,0.9996,0.0005,0.0001</t>
   </si>
   <si>
-    <t>0.0001,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.6617,0.4705,0.0170,0.0005</t>
-  </si>
-  <si>
-    <t>0.1205,0.0210,0.8739,0.0036</t>
-  </si>
-  <si>
-    <t>0.0333,0.0085,0.9659,0.0010</t>
-  </si>
-  <si>
-    <t>0.3404,0.0129,0.6505,0.0025</t>
-  </si>
-  <si>
-    <t>0.1356,0.0172,0.8747,0.0035</t>
-  </si>
-  <si>
-    <t>0.0002,0.6421,0.5133,0.2104</t>
+    <t>0.0001,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.6612,0.4706,0.0171,0.0005</t>
+  </si>
+  <si>
+    <t>0.1198,0.0209,0.8747,0.0036</t>
+  </si>
+  <si>
+    <t>0.0332,0.0085,0.9660,0.0010</t>
+  </si>
+  <si>
+    <t>0.3388,0.0128,0.6525,0.0025</t>
+  </si>
+  <si>
+    <t>0.1345,0.0171,0.8757,0.0035</t>
+  </si>
+  <si>
+    <t>0.0002,0.6411,0.5143,0.2103</t>
   </si>
   <si>
     <t>0.0002,0.9999,0.0010,0.0001</t>
@@ -1192,16 +1192,16 @@
     <t>0.0002,0.9990,0.0010,0.0048</t>
   </si>
   <si>
-    <t>0.0003,0.9992,0.0623,0.0010</t>
-  </si>
-  <si>
-    <t>0.0031,0.9960,0.0535,0.0002</t>
-  </si>
-  <si>
-    <t>0.4461,0.5791,0.0577,0.0020</t>
-  </si>
-  <si>
-    <t>0.1988,0.8365,0.0233,0.0036</t>
+    <t>0.0003,0.9992,0.0625,0.0010</t>
+  </si>
+  <si>
+    <t>0.0031,0.9960,0.0538,0.0002</t>
+  </si>
+  <si>
+    <t>0.4456,0.5789,0.0581,0.0020</t>
+  </si>
+  <si>
+    <t>0.1986,0.8365,0.0235,0.0036</t>
   </si>
   <si>
     <t>0.9970,0.0003,0.0006,0.0003</t>
@@ -1213,7 +1213,7 @@
     <t>0.9905,0.0039,0.0013,0.0008</t>
   </si>
   <si>
-    <t>0.9886,0.0016,0.0044,0.0004</t>
+    <t>0.9885,0.0017,0.0045,0.0004</t>
   </si>
   <si>
     <t>0.9985,0.0003,0.0002,0.0001</t>
@@ -1228,31 +1228,31 @@
     <t>0.9911,0.0010,0.0030,0.0002</t>
   </si>
   <si>
-    <t>0.0003,0.9724,0.9486,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.3966,0.9937,0.0002</t>
+    <t>0.0003,0.9723,0.9487,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.3960,0.9937,0.0002</t>
   </si>
   <si>
     <t>0.0006,0.0241,0.9976,0.0005</t>
   </si>
   <si>
-    <t>0.0056,0.0061,0.9936,0.0001</t>
-  </si>
-  <si>
-    <t>0.9501,0.0016,0.0368,0.0003</t>
-  </si>
-  <si>
-    <t>0.4078,0.3934,0.0734,0.0039</t>
-  </si>
-  <si>
-    <t>0.1649,0.0004,0.9092,0.0004</t>
-  </si>
-  <si>
-    <t>0.8157,0.0038,0.1753,0.0012</t>
-  </si>
-  <si>
-    <t>0.0067,0.0007,0.0017,0.9990</t>
+    <t>0.0056,0.0060,0.9937,0.0001</t>
+  </si>
+  <si>
+    <t>0.9498,0.0016,0.0372,0.0003</t>
+  </si>
+  <si>
+    <t>0.4073,0.3927,0.0740,0.0039</t>
+  </si>
+  <si>
+    <t>0.1647,0.0004,0.9094,0.0004</t>
+  </si>
+  <si>
+    <t>0.8145,0.0038,0.1768,0.0012</t>
+  </si>
+  <si>
+    <t>0.0066,0.0007,0.0017,0.9990</t>
   </si>
   <si>
     <t>0.0000,0.0013,0.0008,1.0000</t>
@@ -1261,73 +1261,73 @@
     <t>0.0001,0.0013,0.0006,1.0000</t>
   </si>
   <si>
-    <t>0.0071,0.0005,0.0014,0.9991</t>
+    <t>0.0070,0.0005,0.0014,0.9991</t>
   </si>
   <si>
     <t>0.0001,0.9889,0.9643,0.0001</t>
   </si>
   <si>
-    <t>0.9818,0.0011,0.0091,0.0003</t>
-  </si>
-  <si>
-    <t>0.0111,0.9865,0.0165,0.0053</t>
+    <t>0.9817,0.0011,0.0091,0.0003</t>
+  </si>
+  <si>
+    <t>0.0111,0.9865,0.0166,0.0053</t>
   </si>
   <si>
     <t>0.9942,0.0006,0.0020,0.0001</t>
   </si>
   <si>
-    <t>0.0162,0.9854,0.0136,0.0010</t>
+    <t>0.0162,0.9854,0.0137,0.0010</t>
   </si>
   <si>
     <t>0.9927,0.0013,0.0011,0.0009</t>
   </si>
   <si>
-    <t>0.8608,0.0000,0.3309,0.0000</t>
-  </si>
-  <si>
-    <t>0.7755,0.0000,0.3904,0.0000</t>
+    <t>0.8604,0.0000,0.3318,0.0000</t>
+  </si>
+  <si>
+    <t>0.7745,0.0000,0.3920,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9488,0.0006,0.0274,0.0005</t>
-  </si>
-  <si>
-    <t>0.9682,0.0217,0.0071,0.0008</t>
-  </si>
-  <si>
-    <t>0.5344,0.3344,0.0338,0.0021</t>
+    <t>0.9486,0.0006,0.0276,0.0005</t>
+  </si>
+  <si>
+    <t>0.9682,0.0217,0.0072,0.0008</t>
+  </si>
+  <si>
+    <t>0.5336,0.3344,0.0340,0.0021</t>
   </si>
   <si>
     <t>0.9898,0.0009,0.0042,0.0001</t>
   </si>
   <si>
-    <t>0.9382,0.0202,0.0174,0.0009</t>
-  </si>
-  <si>
-    <t>0.2159,0.7285,0.0721,0.0170</t>
-  </si>
-  <si>
-    <t>0.9130,0.0195,0.0338,0.0007</t>
-  </si>
-  <si>
-    <t>0.9515,0.0014,0.0374,0.0003</t>
-  </si>
-  <si>
-    <t>0.9943,0.0027,0.0011,0.0002</t>
+    <t>0.9379,0.0201,0.0175,0.0009</t>
+  </si>
+  <si>
+    <t>0.2159,0.7279,0.0725,0.0171</t>
+  </si>
+  <si>
+    <t>0.9125,0.0195,0.0341,0.0007</t>
+  </si>
+  <si>
+    <t>0.9513,0.0014,0.0376,0.0003</t>
+  </si>
+  <si>
+    <t>0.9942,0.0027,0.0011,0.0002</t>
   </si>
   <si>
     <t>0.9958,0.0025,0.0004,0.0004</t>
   </si>
   <si>
-    <t>0.9911,0.0018,0.0025,0.0003</t>
+    <t>0.9910,0.0018,0.0025,0.0003</t>
   </si>
   <si>
     <t>0.9885,0.0015,0.0039,0.0002</t>
   </si>
   <si>
-    <t>0.9940,0.0026,0.0010,0.0001</t>
+    <t>0.9940,0.0026,0.0011,0.0001</t>
   </si>
   <si>
     <t>0.9911,0.0042,0.0016,0.0004</t>
@@ -1339,34 +1339,34 @@
     <t>0.9916,0.0017,0.0019,0.0001</t>
   </si>
   <si>
-    <t>0.6927,0.3733,0.0029,0.0014</t>
-  </si>
-  <si>
-    <t>0.2562,0.7638,0.0288,0.0108</t>
-  </si>
-  <si>
-    <t>0.8518,0.1484,0.0053,0.0009</t>
-  </si>
-  <si>
-    <t>0.9359,0.0430,0.0202,0.0023</t>
+    <t>0.6927,0.3730,0.0029,0.0014</t>
+  </si>
+  <si>
+    <t>0.2556,0.7640,0.0290,0.0108</t>
+  </si>
+  <si>
+    <t>0.8520,0.1480,0.0053,0.0009</t>
+  </si>
+  <si>
+    <t>0.9355,0.0431,0.0204,0.0023</t>
   </si>
   <si>
     <t>0.9855,0.0078,0.0030,0.0001</t>
   </si>
   <si>
-    <t>0.9566,0.0408,0.0050,0.0006</t>
-  </si>
-  <si>
-    <t>0.9867,0.0020,0.0055,0.0002</t>
-  </si>
-  <si>
-    <t>0.9413,0.0281,0.0158,0.0012</t>
+    <t>0.9564,0.0409,0.0051,0.0006</t>
+  </si>
+  <si>
+    <t>0.9866,0.0020,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.9412,0.0281,0.0159,0.0012</t>
   </si>
   <si>
     <t>0.0146,0.0030,0.9908,0.0002</t>
   </si>
   <si>
-    <t>0.9368,0.0468,0.0079,0.0003</t>
+    <t>0.9366,0.0469,0.0079,0.0003</t>
   </si>
   <si>
     <t>0.0007,0.0007,0.9994,0.0000</t>
@@ -1375,10 +1375,10 @@
     <t>0.0004,0.0693,0.9908,0.0046</t>
   </si>
   <si>
-    <t>0.0159,0.0023,0.9875,0.0006</t>
-  </si>
-  <si>
-    <t>0.0027,0.3159,0.9692,0.0008</t>
+    <t>0.0158,0.0023,0.9875,0.0006</t>
+  </si>
+  <si>
+    <t>0.0027,0.3158,0.9693,0.0008</t>
   </si>
   <si>
     <t>0.0021,0.0035,0.9972,0.0002</t>
@@ -1387,34 +1387,34 @@
     <t>0.0020,0.0002,0.9990,0.0000</t>
   </si>
   <si>
-    <t>0.0152,0.0014,0.9896,0.0001</t>
-  </si>
-  <si>
-    <t>0.1148,0.0054,0.9084,0.0008</t>
-  </si>
-  <si>
-    <t>0.1422,0.0020,0.9056,0.0004</t>
-  </si>
-  <si>
-    <t>0.7531,0.0391,0.1485,0.0023</t>
-  </si>
-  <si>
-    <t>0.0699,0.0255,0.8937,0.0015</t>
-  </si>
-  <si>
-    <t>0.0176,0.0536,0.9395,0.0003</t>
-  </si>
-  <si>
-    <t>0.0777,0.0041,0.9388,0.0008</t>
-  </si>
-  <si>
-    <t>0.2604,0.0068,0.7702,0.0030</t>
-  </si>
-  <si>
-    <t>0.6320,0.0412,0.2494,0.0014</t>
-  </si>
-  <si>
-    <t>0.1453,0.9454,0.0068,0.0002</t>
+    <t>0.0151,0.0014,0.9896,0.0001</t>
+  </si>
+  <si>
+    <t>0.1139,0.0054,0.9092,0.0008</t>
+  </si>
+  <si>
+    <t>0.1417,0.0020,0.9060,0.0004</t>
+  </si>
+  <si>
+    <t>0.7523,0.0390,0.1495,0.0024</t>
+  </si>
+  <si>
+    <t>0.0696,0.0254,0.8942,0.0015</t>
+  </si>
+  <si>
+    <t>0.0175,0.0533,0.9399,0.0003</t>
+  </si>
+  <si>
+    <t>0.0774,0.0041,0.9390,0.0008</t>
+  </si>
+  <si>
+    <t>0.2590,0.0068,0.7717,0.0030</t>
+  </si>
+  <si>
+    <t>0.6306,0.0411,0.2512,0.0014</t>
+  </si>
+  <si>
+    <t>0.1453,0.9453,0.0069,0.0002</t>
   </si>
   <si>
     <t>0.0024,0.9979,0.0049,0.0004</t>
@@ -1423,40 +1423,40 @@
     <t>0.0539,0.9621,0.0042,0.0012</t>
   </si>
   <si>
-    <t>0.9760,0.0125,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.3491,0.7638,0.0062,0.0006</t>
-  </si>
-  <si>
-    <t>0.3158,0.6087,0.0243,0.0004</t>
-  </si>
-  <si>
-    <t>0.9576,0.0066,0.0138,0.0002</t>
-  </si>
-  <si>
-    <t>0.3764,0.0434,0.5654,0.0121</t>
-  </si>
-  <si>
-    <t>0.1314,0.0041,0.8924,0.0033</t>
-  </si>
-  <si>
-    <t>0.5871,0.0164,0.3322,0.0028</t>
+    <t>0.9759,0.0125,0.0047,0.0002</t>
+  </si>
+  <si>
+    <t>0.3492,0.7633,0.0063,0.0006</t>
+  </si>
+  <si>
+    <t>0.3156,0.6080,0.0245,0.0004</t>
+  </si>
+  <si>
+    <t>0.9574,0.0066,0.0139,0.0002</t>
+  </si>
+  <si>
+    <t>0.3743,0.0433,0.5679,0.0121</t>
+  </si>
+  <si>
+    <t>0.1310,0.0041,0.8928,0.0033</t>
+  </si>
+  <si>
+    <t>0.5849,0.0163,0.3348,0.0028</t>
   </si>
   <si>
     <t>0.0131,0.0019,0.9893,0.0004</t>
   </si>
   <si>
-    <t>0.1621,0.0051,0.8344,0.0004</t>
-  </si>
-  <si>
-    <t>0.0511,0.0502,0.8729,0.0002</t>
+    <t>0.1608,0.0051,0.8358,0.0004</t>
+  </si>
+  <si>
+    <t>0.0508,0.0501,0.8738,0.0002</t>
   </si>
   <si>
     <t>0.0037,0.0122,0.9932,0.0008</t>
   </si>
   <si>
-    <t>0.0068,0.0086,0.9884,0.0002</t>
+    <t>0.0068,0.0085,0.9884,0.0002</t>
   </si>
   <si>
     <t>0.9953,0.0007,0.0010,0.0001</t>
@@ -1465,16 +1465,16 @@
     <t>0.9811,0.0124,0.0038,0.0007</t>
   </si>
   <si>
-    <t>0.9777,0.0129,0.0027,0.0024</t>
-  </si>
-  <si>
-    <t>0.9896,0.0084,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9575,0.0394,0.0057,0.0020</t>
-  </si>
-  <si>
-    <t>0.9670,0.0358,0.0035,0.0011</t>
+    <t>0.9776,0.0129,0.0027,0.0025</t>
+  </si>
+  <si>
+    <t>0.9896,0.0084,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9575,0.0393,0.0057,0.0020</t>
+  </si>
+  <si>
+    <t>0.9669,0.0358,0.0035,0.0011</t>
   </si>
   <si>
     <t>0.9910,0.0079,0.0011,0.0004</t>
@@ -1483,13 +1483,13 @@
     <t>0.9942,0.0013,0.0013,0.0001</t>
   </si>
   <si>
-    <t>0.0105,0.0034,0.9916,0.0006</t>
-  </si>
-  <si>
-    <t>0.0780,0.0279,0.8845,0.0009</t>
-  </si>
-  <si>
-    <t>0.5255,0.0067,0.4647,0.0117</t>
+    <t>0.0104,0.0034,0.9916,0.0006</t>
+  </si>
+  <si>
+    <t>0.0775,0.0278,0.8854,0.0009</t>
+  </si>
+  <si>
+    <t>0.5236,0.0067,0.4669,0.0117</t>
   </si>
   <si>
     <t>0.0025,0.0008,0.9982,0.0001</t>
@@ -1504,7 +1504,7 @@
     <t>0.0004,0.0000,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0150,0.0080,0.9819,0.0003</t>
+    <t>0.0149,0.0080,0.9819,0.0003</t>
   </si>
   <si>
     <t>0.0001,0.0001,1.0000,0.0000</t>
@@ -1513,43 +1513,43 @@
     <t>0.0048,0.0069,0.9933,0.0004</t>
   </si>
   <si>
-    <t>0.0563,0.0127,0.9347,0.0021</t>
-  </si>
-  <si>
-    <t>0.7920,0.0018,0.2323,0.0009</t>
-  </si>
-  <si>
-    <t>0.5374,0.0015,0.4912,0.0047</t>
-  </si>
-  <si>
-    <t>0.9481,0.0085,0.0205,0.0002</t>
+    <t>0.0560,0.0126,0.9350,0.0021</t>
+  </si>
+  <si>
+    <t>0.7908,0.0018,0.2340,0.0009</t>
+  </si>
+  <si>
+    <t>0.5357,0.0015,0.4933,0.0047</t>
+  </si>
+  <si>
+    <t>0.9479,0.0085,0.0206,0.0002</t>
   </si>
   <si>
     <t>0.9951,0.0023,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.9887,0.0121,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9943,0.0035,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9460,0.0466,0.0049,0.0008</t>
-  </si>
-  <si>
-    <t>0.9938,0.0015,0.0012,0.0001</t>
+    <t>0.9887,0.0120,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0035,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9459,0.0466,0.0049,0.0008</t>
+  </si>
+  <si>
+    <t>0.9937,0.0015,0.0012,0.0001</t>
   </si>
   <si>
     <t>0.9868,0.0123,0.0017,0.0004</t>
   </si>
   <si>
-    <t>0.9952,0.0023,0.0007,0.0002</t>
+    <t>0.9952,0.0024,0.0007,0.0002</t>
   </si>
   <si>
     <t>0.9867,0.0026,0.0035,0.0012</t>
   </si>
   <si>
-    <t>0.0107,0.0203,0.9804,0.0005</t>
+    <t>0.0107,0.0202,0.9804,0.0005</t>
   </si>
   <si>
     <t>0.0014,0.0032,0.9984,0.0000</t>
@@ -1558,37 +1558,37 @@
     <t>0.0029,0.0021,0.9972,0.0000</t>
   </si>
   <si>
-    <t>0.0144,0.0432,0.9562,0.0006</t>
-  </si>
-  <si>
-    <t>0.0141,0.0017,0.9897,0.0001</t>
-  </si>
-  <si>
-    <t>0.7607,0.0793,0.0903,0.0049</t>
-  </si>
-  <si>
-    <t>0.0943,0.0323,0.8579,0.0051</t>
+    <t>0.0143,0.0431,0.9564,0.0006</t>
+  </si>
+  <si>
+    <t>0.0141,0.0017,0.9898,0.0001</t>
+  </si>
+  <si>
+    <t>0.7596,0.0793,0.0910,0.0049</t>
+  </si>
+  <si>
+    <t>0.0937,0.0321,0.8589,0.0050</t>
   </si>
   <si>
     <t>0.0021,0.0007,0.9976,0.0010</t>
   </si>
   <si>
-    <t>0.9731,0.0009,0.0045,0.0032</t>
-  </si>
-  <si>
-    <t>0.0010,0.0045,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.0129,0.0003,0.0011,0.9986</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0033,0.9999</t>
+    <t>0.9729,0.0009,0.0045,0.0032</t>
+  </si>
+  <si>
+    <t>0.0010,0.0044,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0128,0.0003,0.0011,0.9986</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0034,0.9999</t>
   </si>
   <si>
     <t>0.0003,0.0003,0.0012,0.9999</t>
   </si>
   <si>
-    <t>0.7604,0.0139,0.0183,0.1387</t>
+    <t>0.7591,0.0139,0.0184,0.1398</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +1974,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1988,7 +1988,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2030,7 +2030,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2044,7 +2044,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2072,7 +2072,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2086,7 +2086,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2128,7 +2128,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2142,7 +2142,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2156,7 +2156,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2184,7 +2184,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2212,7 +2212,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2240,7 +2240,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2254,7 +2254,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2268,7 +2268,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2282,7 +2282,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2296,7 +2296,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2310,7 +2310,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2338,7 +2338,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2380,7 +2380,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2394,7 +2394,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2408,7 +2408,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2436,7 +2436,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2492,7 +2492,7 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2506,7 +2506,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2520,7 +2520,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2534,7 +2534,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>268</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2618,7 +2618,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2646,7 +2646,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2688,7 +2688,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2702,7 +2702,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2716,7 +2716,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2730,7 +2730,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2744,7 +2744,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2758,7 +2758,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2772,7 +2772,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2786,7 +2786,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2800,7 +2800,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2814,7 +2814,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2828,7 +2828,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2842,7 +2842,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2856,7 +2856,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2870,7 +2870,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2884,7 +2884,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2898,7 +2898,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2912,7 +2912,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3917,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D141" t="s">
         <v>409</v>
